--- a/data/trans_orig/IP2903-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP2903-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24029</t>
+          <t>24361</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39424</t>
+          <t>39465</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16648</t>
+          <t>16889</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28826</t>
+          <t>30802</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43851</t>
+          <t>44988</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64116</t>
+          <t>64550</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17712</t>
+          <t>16997</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31406</t>
+          <t>30619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23835</t>
+          <t>23964</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38638</t>
+          <t>38365</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44523</t>
+          <t>45379</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66364</t>
+          <t>66713</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35705</t>
+          <t>35701</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51819</t>
+          <t>50973</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33179</t>
+          <t>32460</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49122</t>
+          <t>48796</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>73128</t>
+          <t>72960</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>94915</t>
+          <t>95503</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,47%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16755</t>
+          <t>17317</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30029</t>
+          <t>31418</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18813</t>
+          <t>19694</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32482</t>
+          <t>33085</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40697</t>
+          <t>40596</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>59019</t>
+          <t>59420</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28924</t>
+          <t>29381</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15018</t>
+          <t>15051</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28514</t>
+          <t>27772</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>34525</t>
+          <t>34006</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52985</t>
+          <t>53241</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32224</t>
+          <t>31533</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46321</t>
+          <t>46531</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30665</t>
+          <t>29618</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45325</t>
+          <t>44305</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66492</t>
+          <t>65948</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86484</t>
+          <t>86620</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,32%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15924</t>
+          <t>16341</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28536</t>
+          <t>27869</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20299</t>
+          <t>19914</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33555</t>
+          <t>34387</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39175</t>
+          <t>38797</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57757</t>
+          <t>57722</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10427</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21318</t>
+          <t>21666</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20248</t>
+          <t>19730</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33962</t>
+          <t>33868</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32978</t>
+          <t>33364</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50803</t>
+          <t>51409</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21988</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35043</t>
+          <t>34941</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33725</t>
+          <t>33746</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49668</t>
+          <t>50063</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60364</t>
+          <t>59795</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80660</t>
+          <t>80181</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>49,99%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53620</t>
+          <t>51809</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74280</t>
+          <t>74112</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49797</t>
+          <t>49848</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69532</t>
+          <t>70151</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>107888</t>
+          <t>108785</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>137311</t>
+          <t>137226</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,41%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34892</t>
+          <t>34618</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52745</t>
+          <t>52535</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35880</t>
+          <t>35888</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55666</t>
+          <t>56308</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>75559</t>
+          <t>74496</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>100411</t>
+          <t>101562</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>75028</t>
+          <t>76755</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>99971</t>
+          <t>100031</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78870</t>
+          <t>78109</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>100335</t>
+          <t>99831</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>161871</t>
+          <t>160789</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>192901</t>
+          <t>192337</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,62%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30349</t>
+          <t>29798</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46466</t>
+          <t>45850</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44270</t>
+          <t>43789</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60832</t>
+          <t>60867</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78652</t>
+          <t>79090</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101838</t>
+          <t>102170</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,09%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>16656</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14008</t>
+          <t>13900</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27404</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>24182</t>
+          <t>23034</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>40481</t>
+          <t>39553</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41745</t>
+          <t>42935</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58612</t>
+          <t>58857</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42219</t>
+          <t>42864</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59663</t>
+          <t>59985</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>89026</t>
+          <t>90123</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>112826</t>
+          <t>113430</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10795</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22891</t>
+          <t>22168</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19478</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31888</t>
+          <t>31329</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>33154</t>
+          <t>33295</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>50131</t>
+          <t>51031</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>9382</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20800</t>
+          <t>20547</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17642</t>
+          <t>17220</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18272</t>
+          <t>19135</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33268</t>
+          <t>34183</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35283</t>
+          <t>35814</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>49501</t>
+          <t>49740</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>25833</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38961</t>
+          <t>40118</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>66353</t>
+          <t>66701</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>84731</t>
+          <t>85546</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,86%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>176600</t>
+          <t>175460</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>213468</t>
+          <t>211607</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>192658</t>
+          <t>192267</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>230804</t>
+          <t>230794</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>378922</t>
+          <t>378077</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>431546</t>
+          <t>432639</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,95%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>114208</t>
+          <t>115053</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>145250</t>
+          <t>148933</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>138366</t>
+          <t>137164</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>174163</t>
+          <t>173290</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>260308</t>
+          <t>261338</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>310637</t>
+          <t>308880</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>271270</t>
+          <t>270215</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>310717</t>
+          <t>310751</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>272106</t>
+          <t>270961</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>313795</t>
+          <t>312049</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>553928</t>
+          <t>557053</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>612976</t>
+          <t>609961</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,86%</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22194</t>
+          <t>21558</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36568</t>
+          <t>36950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23146</t>
+          <t>22393</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37473</t>
+          <t>36992</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49294</t>
+          <t>49573</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69561</t>
+          <t>70519</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9512</t>
+          <t>9198</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20948</t>
+          <t>20803</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20288</t>
+          <t>19850</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34820</t>
+          <t>34728</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31832</t>
+          <t>31749</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50724</t>
+          <t>50217</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,37%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37444</t>
+          <t>37604</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52295</t>
+          <t>53630</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24716</t>
+          <t>24243</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38350</t>
+          <t>39506</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67802</t>
+          <t>66699</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>88763</t>
+          <t>89912</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,79%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23435</t>
+          <t>23682</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38345</t>
+          <t>37961</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34333</t>
+          <t>33474</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50898</t>
+          <t>49740</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61427</t>
+          <t>61157</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>82187</t>
+          <t>83075</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>45,06%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11870</t>
+          <t>11297</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24275</t>
+          <t>24825</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>15326</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28574</t>
+          <t>28861</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29911</t>
+          <t>29776</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>48392</t>
+          <t>47509</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35324</t>
+          <t>35553</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50532</t>
+          <t>51055</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23182</t>
+          <t>23255</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37790</t>
+          <t>38287</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63057</t>
+          <t>62695</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84606</t>
+          <t>84637</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,91%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28208</t>
+          <t>27401</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42641</t>
+          <t>43233</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22013</t>
+          <t>22075</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35543</t>
+          <t>36804</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>53834</t>
+          <t>53045</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>73469</t>
+          <t>73754</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,66%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9751</t>
+          <t>9898</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22166</t>
+          <t>20967</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17446</t>
+          <t>17934</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31663</t>
+          <t>31139</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30485</t>
+          <t>31118</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49207</t>
+          <t>48967</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,99%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27370</t>
+          <t>27589</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42685</t>
+          <t>42680</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24008</t>
+          <t>23948</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38594</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55364</t>
+          <t>55420</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75606</t>
+          <t>76304</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>45,17%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65174</t>
+          <t>64693</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87545</t>
+          <t>88435</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67457</t>
+          <t>67572</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90891</t>
+          <t>91175</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>139842</t>
+          <t>139185</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172518</t>
+          <t>171802</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26770</t>
+          <t>26644</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44861</t>
+          <t>44108</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33421</t>
+          <t>33224</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52794</t>
+          <t>52859</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64991</t>
+          <t>65444</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>91634</t>
+          <t>91584</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>77751</t>
+          <t>78484</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>102305</t>
+          <t>102978</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>89791</t>
+          <t>87983</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>113069</t>
+          <t>112319</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>173207</t>
+          <t>175478</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>207441</t>
+          <t>208424</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,15%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47905</t>
+          <t>49368</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67641</t>
+          <t>68533</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51073</t>
+          <t>50572</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69935</t>
+          <t>70346</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>104284</t>
+          <t>103549</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>131322</t>
+          <t>131830</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,4%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12582</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26327</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14269</t>
+          <t>13912</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28253</t>
+          <t>28391</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>30263</t>
+          <t>30675</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>49612</t>
+          <t>50576</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58647</t>
+          <t>58885</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>79019</t>
+          <t>78560</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49213</t>
+          <t>48968</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67835</t>
+          <t>68406</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>112125</t>
+          <t>113864</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>141909</t>
+          <t>141979</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,97%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12248</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23002</t>
+          <t>22455</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17281</t>
+          <t>17435</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29943</t>
+          <t>30366</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>32220</t>
+          <t>32161</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>49271</t>
+          <t>48834</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,36%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>9176</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20573</t>
+          <t>20113</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12518</t>
+          <t>12134</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24053</t>
+          <t>24120</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>24693</t>
+          <t>23773</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40688</t>
+          <t>39780</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,06%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15896</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27579</t>
+          <t>27916</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>23766</t>
+          <t>23932</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>36885</t>
+          <t>37333</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>43374</t>
+          <t>42522</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>61052</t>
+          <t>61018</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,18%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>225448</t>
+          <t>223898</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>264892</t>
+          <t>265300</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>240689</t>
+          <t>241561</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>281374</t>
+          <t>281881</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>478513</t>
+          <t>477961</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>537515</t>
+          <t>538199</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,5%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>100044</t>
+          <t>98824</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>132345</t>
+          <t>129763</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>135564</t>
+          <t>134843</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>171452</t>
+          <t>170597</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>244684</t>
+          <t>242828</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>289779</t>
+          <t>291415</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>283337</t>
+          <t>283774</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>326644</t>
+          <t>324554</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>263236</t>
+          <t>260294</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>305454</t>
+          <t>304113</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>558764</t>
+          <t>553738</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>617207</t>
+          <t>617043</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,29%</t>
         </is>
       </c>
     </row>
@@ -7584,12 +7584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11033</t>
+          <t>11465</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24095</t>
+          <t>23258</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12612</t>
+          <t>13006</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25459</t>
+          <t>25643</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27625</t>
+          <t>28299</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44870</t>
+          <t>45961</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16319</t>
+          <t>16105</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29478</t>
+          <t>29335</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19833</t>
+          <t>19602</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33656</t>
+          <t>33615</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39659</t>
+          <t>39667</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58599</t>
+          <t>59363</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35581</t>
+          <t>35993</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50598</t>
+          <t>50483</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41517</t>
+          <t>41268</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57464</t>
+          <t>56534</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>81219</t>
+          <t>80845</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>103103</t>
+          <t>103273</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,42%</t>
         </is>
       </c>
     </row>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24936</t>
+          <t>24935</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21749</t>
+          <t>21938</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36029</t>
+          <t>36599</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49555</t>
+          <t>49805</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71671</t>
+          <t>71855</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24707</t>
+          <t>24993</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39858</t>
+          <t>40554</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24229</t>
+          <t>23176</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39428</t>
+          <t>38628</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>53563</t>
+          <t>52791</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>74025</t>
+          <t>74524</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31527</t>
+          <t>31342</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47102</t>
+          <t>47491</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40144</t>
+          <t>40655</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57255</t>
+          <t>58028</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76191</t>
+          <t>75971</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99855</t>
+          <t>99482</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,96%</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>9817</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20808</t>
+          <t>20813</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15872</t>
+          <t>15789</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28106</t>
+          <t>28362</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28540</t>
+          <t>28643</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>45434</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14649</t>
+          <t>14818</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26169</t>
+          <t>26606</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18139</t>
+          <t>18166</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30922</t>
+          <t>31858</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37138</t>
+          <t>35489</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54701</t>
+          <t>53799</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18631</t>
+          <t>19115</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>31545</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21945</t>
+          <t>22299</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36664</t>
+          <t>36500</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44594</t>
+          <t>45857</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63815</t>
+          <t>63985</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,25%</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51548</t>
+          <t>50798</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72695</t>
+          <t>72593</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49687</t>
+          <t>50184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71576</t>
+          <t>71684</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>107252</t>
+          <t>108008</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136727</t>
+          <t>138320</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45092</t>
+          <t>45275</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65531</t>
+          <t>66378</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>41302</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62301</t>
+          <t>62040</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>93118</t>
+          <t>93519</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>121938</t>
+          <t>123294</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>89340</t>
+          <t>87807</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>111987</t>
+          <t>111847</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>81309</t>
+          <t>81051</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>103906</t>
+          <t>105020</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>176388</t>
+          <t>175926</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>210935</t>
+          <t>209962</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,71%</t>
         </is>
       </c>
     </row>
@@ -9408,12 +9408,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34408</t>
+          <t>34881</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51951</t>
+          <t>51893</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30769</t>
+          <t>30374</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48512</t>
+          <t>47614</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>69251</t>
+          <t>69131</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>95096</t>
+          <t>94726</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33686</t>
+          <t>34370</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51682</t>
+          <t>51579</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28074</t>
+          <t>27789</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>45484</t>
+          <t>46414</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>67627</t>
+          <t>67374</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>91872</t>
+          <t>91518</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38855</t>
+          <t>39348</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56758</t>
+          <t>56880</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53131</t>
+          <t>53493</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73727</t>
+          <t>73003</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>98018</t>
+          <t>97175</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>124183</t>
+          <t>124544</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,82%</t>
         </is>
       </c>
     </row>
@@ -9864,12 +9864,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14076</t>
+          <t>13876</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25828</t>
+          <t>25989</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12508</t>
+          <t>12070</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24305</t>
+          <t>24082</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>28859</t>
+          <t>29423</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>45801</t>
+          <t>46144</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9519</t>
+          <t>9594</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20224</t>
+          <t>20386</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14941</t>
+          <t>15005</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27182</t>
+          <t>26988</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27632</t>
+          <t>27482</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>43391</t>
+          <t>44806</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>35,12%</t>
         </is>
       </c>
     </row>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19636</t>
+          <t>19772</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32392</t>
+          <t>32738</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21995</t>
+          <t>22399</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34931</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>46609</t>
+          <t>46660</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>64909</t>
+          <t>65228</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>51,13%</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10320,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>169169</t>
+          <t>170242</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>207690</t>
+          <t>207463</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>167442</t>
+          <t>168052</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>206261</t>
+          <t>205926</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>346157</t>
+          <t>348455</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>399940</t>
+          <t>403309</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,97%</t>
         </is>
       </c>
     </row>
@@ -10433,12 +10433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>170094</t>
+          <t>169578</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>207025</t>
+          <t>206026</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>171852</t>
+          <t>172354</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>211151</t>
+          <t>209650</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>351957</t>
+          <t>354696</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>404386</t>
+          <t>405382</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>259168</t>
+          <t>259808</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>299904</t>
+          <t>301215</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>289252</t>
+          <t>291312</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>332695</t>
+          <t>334142</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>567099</t>
+          <t>565238</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>624243</t>
+          <t>622290</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,24%</t>
         </is>
       </c>
     </row>
